--- a/TIMES-NZ/v303/VT_TIMESNZ_PRI.xlsx
+++ b/TIMES-NZ/v303/VT_TIMESNZ_PRI.xlsx
@@ -8,11 +8,12 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Natural Gas" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Oil" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Coal" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Total CO2" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Biofuels" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Hydrogen" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gas Distribution" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Oil" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Coal" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Total CO2" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Biofuels" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Hydrogen" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -422,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G123"/>
+  <dimension ref="A1:G131"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -553,6 +554,11 @@
           <t>Tcap</t>
         </is>
       </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Region</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -575,6 +581,11 @@
           <t>PJa</t>
         </is>
       </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>NI</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -597,6 +608,11 @@
           <t>PJa</t>
         </is>
       </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>NI</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
@@ -731,12 +747,12 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>GasSupplyForecasts</t>
+          <t>GasSupplyHistorical</t>
         </is>
       </c>
       <c r="B19" s="1" t="inlineStr">
         <is>
-          <t>Add natural gas production forecast limits. Excludes contingent - only the 2P reserves.</t>
+          <t>Hardcoded gas production limits for fields according to historical net outputs. Should code this from historical.</t>
         </is>
       </c>
     </row>
@@ -750,198 +766,135 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
+          <t>Attribute</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
           <t>TechName</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="C21" t="inlineStr">
         <is>
           <t>Year</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
+      <c r="D21" t="inlineStr">
         <is>
           <t>NI</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>Attribute</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
+          <t>ACT_BND</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
           <t>MINNGA-KAP</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>11.5381806550665</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>ACT_BND</t>
-        </is>
+      <c r="C22" t="n">
+        <v>2023</v>
+      </c>
+      <c r="D22" t="n">
+        <v>12.11</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
+          <t>ACT_BND</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
           <t>MINNGA-KAP</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>10.375493383123</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>ACT_BND</t>
-        </is>
+      <c r="C23" t="n">
+        <v>2024</v>
+      </c>
+      <c r="D23" t="n">
+        <v>14.24</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>MINNGA-KAP</t>
+          <t>ACT_BND</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2027</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>10.7468780725337</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>ACT_BND</t>
-        </is>
+          <t>MINNGA-OTH</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>2023</v>
+      </c>
+      <c r="D24" t="n">
+        <v>135.94</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>MINNGA-KAP</t>
+          <t>ACT_BND</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2028</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>9.1917409276436</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>ACT_BND</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>MINNGA-KAP</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>2029</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>8.19761893688904</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>ACT_BND</t>
-        </is>
+          <t>MINNGA-OTH</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>2024</v>
+      </c>
+      <c r="D25" t="n">
+        <v>104.73</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>MINNGA-KAP</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>2030</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>7.53384347739316</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>ACT_BND</t>
+      <c r="A27" s="1" t="inlineStr">
+        <is>
+          <t>GasSupplyForecasts</t>
+        </is>
+      </c>
+      <c r="B27" s="1" t="inlineStr">
+        <is>
+          <t>Add natural gas production forecast limits. Excludes contingent - only the 2P reserves.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>MINNGA-KAP</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>2031</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>6.5895965067794</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>ACT_BND</t>
+          <t>~FI_T</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>MINNGA-KAP</t>
+          <t>TechName</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2032</t>
+          <t>Year</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>5.96277081680254</t>
+          <t>NI</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>ACT_BND</t>
+          <t>Attribute</t>
         </is>
       </c>
     </row>
@@ -953,12 +906,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2033</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>5.05229862598231</t>
+          <t>11.5381806550665</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -975,12 +928,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2034</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>4.6329697976859</t>
+          <t>10.375493383123</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -997,12 +950,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2035</t>
+          <t>2027</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>4.00178668858872</t>
+          <t>10.7468780725337</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -1019,12 +972,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2036</t>
+          <t>2028</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>3.64747375910024</t>
+          <t>9.1917409276436</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -1041,12 +994,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2037</t>
+          <t>2029</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>2.86032717495634</t>
+          <t>8.19761893688904</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -1063,12 +1016,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2038</t>
+          <t>2030</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>2.37123019368736</t>
+          <t>7.53384347739316</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -1085,12 +1038,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2039</t>
+          <t>2031</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>6.5895965067794</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -1107,12 +1060,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2040</t>
+          <t>2032</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.96277081680254</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -1129,12 +1082,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2041</t>
+          <t>2033</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.05229862598231</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -1151,12 +1104,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2042</t>
+          <t>2034</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>4.6329697976859</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -1173,12 +1126,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2043</t>
+          <t>2035</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>4.00178668858872</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -1195,12 +1148,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2044</t>
+          <t>2036</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.64747375910024</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -1217,12 +1170,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2045</t>
+          <t>2037</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.86032717495634</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -1239,12 +1192,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2046</t>
+          <t>2038</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.37123019368736</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -1261,7 +1214,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2047</t>
+          <t>2039</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1283,7 +1236,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2048</t>
+          <t>2040</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1305,7 +1258,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2049</t>
+          <t>2041</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -1327,7 +1280,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2050</t>
+          <t>2042</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -1349,7 +1302,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2051</t>
+          <t>2043</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -1371,7 +1324,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2052</t>
+          <t>2044</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -1393,7 +1346,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2053</t>
+          <t>2045</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -1415,7 +1368,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2054</t>
+          <t>2046</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -1437,7 +1390,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2055</t>
+          <t>2047</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -1459,7 +1412,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>2056</t>
+          <t>2048</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -1481,7 +1434,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>2057</t>
+          <t>2049</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -1503,7 +1456,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>2058</t>
+          <t>2050</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -1525,7 +1478,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>2059</t>
+          <t>2051</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -1547,7 +1500,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>2060</t>
+          <t>2052</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -1569,7 +1522,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>2061</t>
+          <t>2053</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -1591,7 +1544,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>2062</t>
+          <t>2054</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -1613,7 +1566,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>2063</t>
+          <t>2055</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -1635,7 +1588,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>2064</t>
+          <t>2056</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -1657,7 +1610,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>2065</t>
+          <t>2057</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -1679,7 +1632,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>2066</t>
+          <t>2058</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -1701,7 +1654,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>2067</t>
+          <t>2059</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -1723,7 +1676,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>2068</t>
+          <t>2060</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -1745,7 +1698,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>2069</t>
+          <t>2061</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -1767,7 +1720,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>2070</t>
+          <t>2062</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -1789,7 +1742,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>2071</t>
+          <t>2063</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -1811,7 +1764,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>2072</t>
+          <t>2064</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -1833,7 +1786,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>2073</t>
+          <t>2065</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -1855,7 +1808,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>2074</t>
+          <t>2066</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -1877,7 +1830,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>2075</t>
+          <t>2067</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -1894,17 +1847,17 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>MINNGA-OTH</t>
+          <t>MINNGA-KAP</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2068</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>95.24587658503351</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -1916,17 +1869,17 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>MINNGA-OTH</t>
+          <t>MINNGA-KAP</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2069</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>89.57779334938446</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -1938,17 +1891,17 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>MINNGA-OTH</t>
+          <t>MINNGA-KAP</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>2027</t>
+          <t>2070</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>84.07928072493367</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -1960,17 +1913,17 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>MINNGA-OTH</t>
+          <t>MINNGA-KAP</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>2028</t>
+          <t>2071</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>71.42455192787747</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -1982,17 +1935,17 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>MINNGA-OTH</t>
+          <t>MINNGA-KAP</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>2072</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>65.59725023625958</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -2004,17 +1957,17 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>MINNGA-OTH</t>
+          <t>MINNGA-KAP</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>2073</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>59.27218902890522</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -2026,17 +1979,17 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>MINNGA-OTH</t>
+          <t>MINNGA-KAP</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>2031</t>
+          <t>2074</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>53.96237273875011</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -2048,17 +2001,17 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>MINNGA-OTH</t>
+          <t>MINNGA-KAP</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>2032</t>
+          <t>2075</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>50.247806934636486</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -2075,12 +2028,12 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>2033</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>45.37624459079853</t>
+          <t>95.24587658503351</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -2097,12 +2050,12 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>2034</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>39.166433727785055</t>
+          <t>89.57779334938446</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -2119,12 +2072,12 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>2035</t>
+          <t>2027</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>30.86048431873355</t>
+          <t>84.07928072493367</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -2141,12 +2094,12 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>2036</t>
+          <t>2028</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>25.730782331146322</t>
+          <t>71.42455192787747</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -2163,12 +2116,12 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>2037</t>
+          <t>2029</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>22.09579918495426</t>
+          <t>65.59725023625958</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -2185,12 +2138,12 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>2038</t>
+          <t>2030</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>19.49424990814645</t>
+          <t>59.27218902890522</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -2207,12 +2160,12 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>2039</t>
+          <t>2031</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>17.24646413752621</t>
+          <t>53.96237273875011</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -2229,12 +2182,12 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>2040</t>
+          <t>2032</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>15.4813259096997</t>
+          <t>50.247806934636486</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -2251,12 +2204,12 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>2041</t>
+          <t>2033</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>14.02004048538556</t>
+          <t>45.37624459079853</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -2273,12 +2226,12 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>2042</t>
+          <t>2034</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>12.84114648218629</t>
+          <t>39.166433727785055</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -2295,12 +2248,12 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>2043</t>
+          <t>2035</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>11.82097058077913</t>
+          <t>30.86048431873355</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -2317,12 +2270,12 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>2044</t>
+          <t>2036</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>6.50124832875542</t>
+          <t>25.730782331146322</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -2339,12 +2292,12 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>2045</t>
+          <t>2037</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>5.899561588189989</t>
+          <t>22.09579918495426</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -2361,12 +2314,12 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>2046</t>
+          <t>2038</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>5.35248596836225</t>
+          <t>19.49424990814645</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -2383,12 +2336,12 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>2047</t>
+          <t>2039</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>4.78924295634605</t>
+          <t>17.24646413752621</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -2405,12 +2358,12 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>2048</t>
+          <t>2040</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>4.3584815595707305</t>
+          <t>15.4813259096997</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -2427,12 +2380,12 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>2049</t>
+          <t>2041</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>3.88311794382764</t>
+          <t>14.02004048538556</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -2449,12 +2402,12 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>2050</t>
+          <t>2042</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>3.29543106110618</t>
+          <t>12.84114648218629</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -2471,12 +2424,12 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>2051</t>
+          <t>2043</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>2.93711977840286</t>
+          <t>11.82097058077913</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -2493,12 +2446,12 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>2052</t>
+          <t>2044</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>2.4877187177274</t>
+          <t>6.50124832875542</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -2515,12 +2468,12 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>2053</t>
+          <t>2045</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>1.81312606372102</t>
+          <t>5.899561588189989</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -2537,12 +2490,12 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>2054</t>
+          <t>2046</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>1.1071870523033198</t>
+          <t>5.35248596836225</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -2559,12 +2512,12 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>2055</t>
+          <t>2047</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>0.14076190535498</t>
+          <t>4.78924295634605</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -2581,12 +2534,12 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>2056</t>
+          <t>2048</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>0.07072071887365</t>
+          <t>4.3584815595707305</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -2603,12 +2556,12 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>2057</t>
+          <t>2049</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>0.06743662337085</t>
+          <t>3.88311794382764</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -2625,12 +2578,12 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>2058</t>
+          <t>2050</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>0.06453896072369</t>
+          <t>3.29543106110618</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -2647,12 +2600,12 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>2059</t>
+          <t>2051</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>0.061815223472539996</t>
+          <t>2.93711977840286</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -2669,12 +2622,12 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>2060</t>
+          <t>2052</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>0.059410935620290005</t>
+          <t>2.4877187177274</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -2691,12 +2644,12 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>2061</t>
+          <t>2053</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>0.05683066548064</t>
+          <t>1.81312606372102</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -2713,12 +2666,12 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>2062</t>
+          <t>2054</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>0.0545534544871</t>
+          <t>1.1071870523033198</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -2735,12 +2688,12 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>2063</t>
+          <t>2055</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>0.05240352373058</t>
+          <t>0.14076190535498</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -2757,12 +2710,12 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>2064</t>
+          <t>2056</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>0.05050707187168</t>
+          <t>0.07072071887365</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -2779,12 +2732,12 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>2065</t>
+          <t>2057</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>0.048444711551749994</t>
+          <t>0.06743662337085</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -2801,12 +2754,12 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>2066</t>
+          <t>2058</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>0.046625306445100004</t>
+          <t>0.06453896072369</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -2823,12 +2776,12 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>2067</t>
+          <t>2059</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>0.04490117431357</t>
+          <t>0.061815223472539996</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -2845,12 +2798,12 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>2068</t>
+          <t>2060</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>0.043382307728640004</t>
+          <t>0.059410935620290005</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -2867,12 +2820,12 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>2069</t>
+          <t>2061</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>0.04170960538514</t>
+          <t>0.05683066548064</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -2889,12 +2842,12 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>2070</t>
+          <t>2062</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>0.040235281846660004</t>
+          <t>0.0545534544871</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -2911,12 +2864,12 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>2071</t>
+          <t>2063</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>0.03883364936868</t>
+          <t>0.05240352373058</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -2933,12 +2886,12 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>2072</t>
+          <t>2064</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>0.037601106557390004</t>
+          <t>0.05050707187168</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -2955,12 +2908,12 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>2073</t>
+          <t>2065</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>0.03622713569939</t>
+          <t>0.048444711551749994</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -2977,12 +2930,12 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>2074</t>
+          <t>2066</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>0.035017687338399994</t>
+          <t>0.046625306445100004</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -2999,15 +2952,191 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
+          <t>2067</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>0.04490117431357</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>ACT_BND</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>MINNGA-OTH</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>2068</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>0.043382307728640004</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>ACT_BND</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>MINNGA-OTH</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>2069</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>0.04170960538514</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>ACT_BND</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>MINNGA-OTH</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>2070</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>0.040235281846660004</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>ACT_BND</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>MINNGA-OTH</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>2071</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>0.03883364936868</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>ACT_BND</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>MINNGA-OTH</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>2072</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>0.037601106557390004</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>ACT_BND</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>MINNGA-OTH</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>2073</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>0.03622713569939</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>ACT_BND</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>MINNGA-OTH</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>2074</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>0.035017687338399994</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>ACT_BND</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>MINNGA-OTH</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
           <t>2075</t>
         </is>
       </c>
-      <c r="C123" t="inlineStr">
+      <c r="C131" t="inlineStr">
         <is>
           <t>0.0338646196136</t>
         </is>
       </c>
-      <c r="D123" t="inlineStr">
+      <c r="D131" t="inlineStr">
         <is>
           <t>ACT_BND</t>
         </is>
@@ -3019,6 +3148,352 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G21"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>GasDistributionCommodities</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Defines distributed gas commodities</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>~FI_Comm</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>CSets</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>CommName</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LimType</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>NRG</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>NGADD</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>PJ</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>FX</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>NRG</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>BIMDD</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>PJ</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>FX</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>GasDistributionNetworkDeclaration</t>
+        </is>
+      </c>
+      <c r="B7" s="1" t="inlineStr">
+        <is>
+          <t>Defines gas distribution network</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>~FI_Process</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Sets</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>TechName</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Tact</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Tcap</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>PRE</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>G_NGA_DIST</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>PJ</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Pja</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>GasDistributionNetworkParameters</t>
+        </is>
+      </c>
+      <c r="B12" s="1" t="inlineStr">
+        <is>
+          <t>Defines gas distribution network</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>~FI_Process</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Sets</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>TechName</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Region</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NCAP_PASTI</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>CAP2ACT</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>FIXOM</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Life</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>PRE</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>G_NGA_DIST</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>NI</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>150</v>
+      </c>
+      <c r="E15" t="n">
+        <v>1</v>
+      </c>
+      <c r="F15" t="n">
+        <v>200</v>
+      </c>
+      <c r="G15" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>GasDistributionNetworkTopology</t>
+        </is>
+      </c>
+      <c r="B17" s="1" t="inlineStr">
+        <is>
+          <t>Defines In/Out for network. Note that flo_eff must be set in base constraints or this will turn gas into biomethane for free</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>~FI_T</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>TechName</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Comm-IN</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Comm-OUT</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Ceff</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Region</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>G_NGA_DIST</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>NGA</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>NGADD</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>1</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>NI</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>G_NGA_DIST</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>BIM</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>BIMDD</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>1</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>NI</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3718,7 +4193,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3940,7 +4415,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4099,7 +4574,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -12368,7 +12843,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
